--- a/题库/PY程序设计模拟题5.xlsx
+++ b/题库/PY程序设计模拟题5.xlsx
@@ -162,12 +162,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>下面代码的输出结果是（）。</t>
     </r>
     <r>
@@ -179,7 +173,7 @@
       </rPr>
       <t xml:space="preserve">
 x = 1
-x *= 3 + 5 * x * 2
+x *= 3 + 5 * * 2
 print(x)</t>
     </r>
   </si>
